--- a/app/data/weapons_with_tiers.xlsx
+++ b/app/data/weapons_with_tiers.xlsx
@@ -22281,7 +22281,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S96"/>
+  <dimension ref="A1:S101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22411,7 +22411,9 @@
       <c r="G2" t="n">
         <v>10</v>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
       <c r="I2" t="n">
         <v>0.3</v>
       </c>
@@ -22486,7 +22488,9 @@
       <c r="G3" t="n">
         <v>20</v>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
       <c r="I3" t="n">
         <v>0.3</v>
       </c>
@@ -22561,7 +22565,9 @@
       <c r="G4" t="n">
         <v>40</v>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
       <c r="I4" t="n">
         <v>0.3</v>
       </c>
@@ -22641,7 +22647,9 @@
       <c r="G5" t="n">
         <v>80</v>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
       <c r="I5" t="n">
         <v>0.3</v>
       </c>
@@ -22722,7 +22730,9 @@
       <c r="G6" t="n">
         <v>160</v>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
       <c r="I6" t="n">
         <v>0.3</v>
       </c>
@@ -22804,7 +22814,9 @@
       <c r="G7" t="n">
         <v>70</v>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
       <c r="I7" t="n">
         <v>0.45</v>
       </c>
@@ -22879,7 +22891,9 @@
       <c r="G8" t="n">
         <v>140</v>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
       <c r="I8" t="n">
         <v>0.45</v>
       </c>
@@ -22954,7 +22968,9 @@
       <c r="G9" t="n">
         <v>280</v>
       </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
       <c r="I9" t="n">
         <v>0.45</v>
       </c>
@@ -23034,7 +23050,9 @@
       <c r="G10" t="n">
         <v>560</v>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
       <c r="I10" t="n">
         <v>0.45</v>
       </c>
@@ -23115,7 +23133,9 @@
       <c r="G11" t="n">
         <v>1120</v>
       </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
       <c r="I11" t="n">
         <v>0.45</v>
       </c>
@@ -23197,7 +23217,9 @@
       <c r="G12" t="n">
         <v>200</v>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
       <c r="I12" t="n">
         <v>0.55</v>
       </c>
@@ -23272,7 +23294,9 @@
       <c r="G13" t="n">
         <v>400</v>
       </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
       <c r="I13" t="n">
         <v>0.55</v>
       </c>
@@ -23347,7 +23371,9 @@
       <c r="G14" t="n">
         <v>800</v>
       </c>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
       <c r="I14" t="n">
         <v>0.55</v>
       </c>
@@ -23427,7 +23453,9 @@
       <c r="G15" t="n">
         <v>1600</v>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
       <c r="I15" t="n">
         <v>0.55</v>
       </c>
@@ -23508,7 +23536,9 @@
       <c r="G16" t="n">
         <v>3200</v>
       </c>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
       <c r="I16" t="n">
         <v>0.55</v>
       </c>
@@ -28829,7 +28859,9 @@
       <c r="G82" t="n">
         <v>80</v>
       </c>
-      <c r="H82" t="inlineStr"/>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
       <c r="I82" t="n">
         <v>0.45</v>
       </c>
@@ -28904,7 +28936,9 @@
       <c r="G83" t="n">
         <v>160</v>
       </c>
-      <c r="H83" t="inlineStr"/>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
       <c r="I83" t="n">
         <v>0.45</v>
       </c>
@@ -28979,7 +29013,9 @@
       <c r="G84" t="n">
         <v>320</v>
       </c>
-      <c r="H84" t="inlineStr"/>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
       <c r="I84" t="n">
         <v>0.45</v>
       </c>
@@ -29059,7 +29095,9 @@
       <c r="G85" t="n">
         <v>640</v>
       </c>
-      <c r="H85" t="inlineStr"/>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
       <c r="I85" t="n">
         <v>0.45</v>
       </c>
@@ -29140,7 +29178,9 @@
       <c r="G86" t="n">
         <v>1280</v>
       </c>
-      <c r="H86" t="inlineStr"/>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
       <c r="I86" t="n">
         <v>0.45</v>
       </c>
@@ -29222,7 +29262,9 @@
       <c r="G87" t="n">
         <v>100</v>
       </c>
-      <c r="H87" t="inlineStr"/>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
       <c r="I87" t="n">
         <v>2</v>
       </c>
@@ -29297,7 +29339,9 @@
       <c r="G88" t="n">
         <v>200</v>
       </c>
-      <c r="H88" t="inlineStr"/>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
       <c r="I88" t="n">
         <v>2</v>
       </c>
@@ -29372,7 +29416,9 @@
       <c r="G89" t="n">
         <v>400</v>
       </c>
-      <c r="H89" t="inlineStr"/>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
       <c r="I89" t="n">
         <v>2</v>
       </c>
@@ -29452,7 +29498,9 @@
       <c r="G90" t="n">
         <v>800</v>
       </c>
-      <c r="H90" t="inlineStr"/>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
       <c r="I90" t="n">
         <v>2</v>
       </c>
@@ -29533,7 +29581,9 @@
       <c r="G91" t="n">
         <v>1600</v>
       </c>
-      <c r="H91" t="inlineStr"/>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
       <c r="I91" t="n">
         <v>2</v>
       </c>
@@ -29615,7 +29665,9 @@
       <c r="G92" t="n">
         <v>10</v>
       </c>
-      <c r="H92" t="inlineStr"/>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
       <c r="I92" t="n">
         <v>0.1</v>
       </c>
@@ -29690,7 +29742,9 @@
       <c r="G93" t="n">
         <v>20</v>
       </c>
-      <c r="H93" t="inlineStr"/>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
       <c r="I93" t="n">
         <v>0.1</v>
       </c>
@@ -29765,7 +29819,9 @@
       <c r="G94" t="n">
         <v>40</v>
       </c>
-      <c r="H94" t="inlineStr"/>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
       <c r="I94" t="n">
         <v>0.1</v>
       </c>
@@ -29845,7 +29901,9 @@
       <c r="G95" t="n">
         <v>80</v>
       </c>
-      <c r="H95" t="inlineStr"/>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
       <c r="I95" t="n">
         <v>0.1</v>
       </c>
@@ -29926,7 +29984,9 @@
       <c r="G96" t="n">
         <v>160</v>
       </c>
-      <c r="H96" t="inlineStr"/>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
       <c r="I96" t="n">
         <v>0.1</v>
       </c>
@@ -29978,6 +30038,409 @@
         </is>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>ranged-19</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Mágica</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Arremessar Feitiço</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Arremessar Feitiço</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Perfuração</t>
+        </is>
+      </c>
+      <c r="L97" t="n">
+        <v>12</v>
+      </c>
+      <c r="M97" t="n">
+        <v>2</v>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>IQ x 10</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>IQ x 15</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>Magia base para feitiços do tipo Projétil.</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>Comum</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>ranged-19</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Mágica</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Arremessar Feitiço</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Arremessar Feitiço</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Perfuração</t>
+        </is>
+      </c>
+      <c r="L98" t="n">
+        <v>11</v>
+      </c>
+      <c r="M98" t="n">
+        <v>3</v>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>IQ x 10</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>IQ x 15</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>Magia base para feitiços do tipo Projétil.</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>ranged-19</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Mágica</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Arremessar Feitiço</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Arremessar Feitiço</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>1</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Perfuração</t>
+        </is>
+      </c>
+      <c r="L99" t="n">
+        <v>10</v>
+      </c>
+      <c r="M99" t="n">
+        <v>4</v>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>IQ x 10</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>IQ x 15</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>Magia base para feitiços do tipo Projétil.</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>Superior</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+- +1 em testes de Saque Rápido com esta arma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>ranged-19</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Mágica</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Arremessar Feitiço</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Arremessar Feitiço</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>2</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Perfuração</t>
+        </is>
+      </c>
+      <c r="L100" t="n">
+        <v>9</v>
+      </c>
+      <c r="M100" t="n">
+        <v>5</v>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>IQ x 10</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>IQ x 15</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>Magia base para feitiços do tipo Projétil.</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>Excelente</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+- +1 em testes de Saque Rápido com esta arma.
+- +1 em Recarga Rápida com esta arma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>ranged-19</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Mágica</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Arremessar Feitiço</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Arremessar Feitiço</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>3</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Perfuração</t>
+        </is>
+      </c>
+      <c r="L101" t="n">
+        <v>8</v>
+      </c>
+      <c r="M101" t="n">
+        <v>6</v>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>IQ x 10</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>IQ x 15</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>Magia base para feitiços do tipo Projétil.</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>Obra-Prima</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+- +1 em testes de Saque Rápido com esta arma.
+- +1 em Recarga Rápida com esta arma.
+- +1 na perícia relacionada à arma.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
